--- a/membership_registration_forms/024_regional_officer_registration--membership_registration_forms.xlsx
+++ b/membership_registration_forms/024_regional_officer_registration--membership_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1114,8 +1114,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="21" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1143,12 +1143,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'north',_'label':_'north'}</t>
+          <t>north</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'North', 'label': 'North'}</t>
+          <t>North</t>
         </is>
       </c>
     </row>
@@ -1160,12 +1160,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'south',_'label':_'south'}</t>
+          <t>south</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'South', 'label': 'South'}</t>
+          <t>South</t>
         </is>
       </c>
     </row>
@@ -1177,12 +1177,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'east',_'label':_'east'}</t>
+          <t>east</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'East', 'label': 'East'}</t>
+          <t>East</t>
         </is>
       </c>
     </row>
@@ -1194,12 +1194,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'west',_'label':_'west'}</t>
+          <t>west</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'West', 'label': 'West'}</t>
+          <t>West</t>
         </is>
       </c>
     </row>
@@ -1211,12 +1211,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'chairperson',_'label':_'chairperson'}</t>
+          <t>chairperson</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Chairperson', 'label': 'Chairperson'}</t>
+          <t>Chairperson</t>
         </is>
       </c>
     </row>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'vice-chairperson',_'label':_'vice-chairperson'}</t>
+          <t>vice-chairperson</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Vice-Chairperson', 'label': 'Vice-Chairperson'}</t>
+          <t>Vice-Chairperson</t>
         </is>
       </c>
     </row>
@@ -1245,12 +1245,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'member',_'label':_'member'}</t>
+          <t>member</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Member', 'label': 'Member'}</t>
+          <t>Member</t>
         </is>
       </c>
     </row>
@@ -1262,12 +1262,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'agree',_'name':_'agree_terms'}</t>
+          <t>agree</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Agree', 'name': 'agree_terms'}</t>
+          <t>Agree</t>
         </is>
       </c>
     </row>
@@ -1279,12 +1279,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'disagree',_'name':_'disagree_terms'}</t>
+          <t>disagree</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Disagree', 'name': 'disagree_terms'}</t>
+          <t>Disagree</t>
         </is>
       </c>
     </row>
